--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260708.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.64%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>3,483,000</t>
+          <t>3,590,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -704,29 +704,29 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>32,516,000</t>
+          <t>9,501,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -748,73 +748,73 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>9,070,000</t>
+          <t>5,382,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,382,000</t>
+          <t>32,516,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>32,918,000</t>
+          <t>4,071,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -836,112 +836,112 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>3,790,000</t>
+          <t>2,609,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,609,000</t>
+          <t>32,918,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>28,640,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,972,000</t>
+          <t>28,640,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>19,313,000</t>
+          <t>17,008,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>17,008,000</t>
+          <t>1,946,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,242 +975,242 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,946,000</t>
+          <t>32,659,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>32,659,000</t>
+          <t>8,532,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>8,532,000</t>
+          <t>19,313,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,456,000</t>
+          <t>13,608,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>13,608,000</t>
+          <t>19,261,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,670,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>19,261,000</t>
+          <t>8,456,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>12,938,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5,666,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1232,95 +1232,95 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,206,000</t>
+          <t>12,938,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>12,723,000</t>
+          <t>5,983,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>36,477,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,983,000</t>
+          <t>13,206,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1364,29 +1364,29 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8,699,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1474,117 +1474,117 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,065,000</t>
+          <t>475,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>475,000</t>
+          <t>8,065,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>17,290,000</t>
+          <t>44,393,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>44,393,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>17,290,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1635,61 +1635,61 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,314,897,177</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>15,796,000</t>
+          <t>1,306,977,177</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1738,29 +1738,29 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>PB_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>PAYABLES</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7,707,185</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-15,893,968,361</t>
+          <t>-5,934,428,934</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-11.55%</t>
+          <t>-4.32%</t>
         </is>
       </c>
     </row>
